--- a/template/export/TotalStock.xlsx
+++ b/template/export/TotalStock.xlsx
@@ -1,19 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repository\Freelance\inventory-system-backend\template\export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED68B51-CFC6-4E95-9BFE-56531D405726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5581CBE-0A02-47F2-99E1-B7E0691760B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="GUDANG GARAM" sheetId="1" r:id="rId1"/>
+    <sheet name="SAMPOERNA" sheetId="2" r:id="rId2"/>
+    <sheet name="DJARUM" sheetId="3" r:id="rId3"/>
+    <sheet name="BRAND KECIL" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,33 +28,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="5">
   <si>
-    <t>ID</t>
+    <t>CATEGORY</t>
   </si>
   <si>
-    <t>Nama Produk</t>
+    <t>ITEM</t>
   </si>
   <si>
-    <t>Gudang</t>
+    <t>KARTON</t>
   </si>
   <si>
-    <t>Perusahaan</t>
+    <t>BAL</t>
   </si>
   <si>
-    <t>Rak</t>
-  </si>
-  <si>
-    <t>Satuan</t>
-  </si>
-  <si>
-    <t>Kuantiti</t>
-  </si>
-  <si>
-    <t>Stock Minimum</t>
-  </si>
-  <si>
-    <t>Category</t>
+    <t>SLOP</t>
   </si>
 </sst>
 </file>
@@ -369,41 +360,114 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:I2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2A38A65-4DF1-4ABF-A629-A5F2DE9414A6}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" t="s">
-        <v>7</v>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD2F2D8-708B-4D8B-B05E-8A17572C0D1B}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E10F15-F1E2-464C-870F-DA3AF9F1C857}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/template/export/TotalStock.xlsx
+++ b/template/export/TotalStock.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repository\Freelance\inventory-system-backend\template\export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Freelance\Inventory System\inventory-system-backend\template\export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5581CBE-0A02-47F2-99E1-B7E0691760B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3663DF5-2D6E-4B84-9477-A41DD47C0279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GUDANG GARAM" sheetId="1" r:id="rId1"/>
@@ -49,8 +49,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -66,7 +74,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -74,12 +82,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -361,28 +385,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -394,22 +418,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2A38A65-4DF1-4ABF-A629-A5F2DE9414A6}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -421,25 +445,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD2F2D8-708B-4D8B-B05E-8A17572C0D1B}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -451,26 +475,30 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E10F15-F1E2-464C-870F-DA3AF9F1C857}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>